--- a/reporte_envios.xlsx
+++ b/reporte_envios.xlsx
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46177.78373029412</v>
+        <v>46190.68639241702</v>
       </c>
     </row>
   </sheetData>

--- a/reporte_envios.xlsx
+++ b/reporte_envios.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,21 +445,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1234@gmail.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46190.7403242299</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46190.74034189471</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Pedro</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>python@gmail.com</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>46190.68639241702</v>
+      <c r="D4" s="1" t="n">
+        <v>46190.74036078648</v>
       </c>
     </row>
   </sheetData>
